--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>112538742</v>
       </c>
       <c r="B8" t="n">
-        <v>56513</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583053</v>
+        <v>583054</v>
       </c>
       <c r="R8" t="n">
         <v>6968671</v>

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>112538742</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>112538742</v>
       </c>
       <c r="B8" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -1290,7 +1290,7 @@
         <v>112538742</v>
       </c>
       <c r="B8" t="n">
-        <v>57487</v>
+        <v>57490</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1999,6 +1999,1786 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126189733</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91232</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>583010</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6968843</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126189626</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>583055</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6968770</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126189663</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80110</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>583097</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6968518</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ca 3x5cm bål</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126189590</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>583048</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6968633</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126189623</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>583115</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6968621</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126189622</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>583019</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6968674</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126189624</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>583110</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6968680</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126189627</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>583059</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6968767</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126189591</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>583075</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6968803</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126189625</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>583049</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6968768</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126189664</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80075</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>583097</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6968518</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt på sälg</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126189620</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>583033</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6968690</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126189661</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80075</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>583067</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6968526</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ca 10x10 cm bål på björk</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126189621</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>583027</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6968681</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126189628</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>583041</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6968875</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ca 1x1m smockfullt</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -2004,7 +2004,7 @@
         <v>126189733</v>
       </c>
       <c r="B15" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>126189626</v>
       </c>
       <c r="B16" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>126189663</v>
       </c>
       <c r="B17" t="n">
-        <v>80110</v>
+        <v>80111</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>126189590</v>
       </c>
       <c r="B18" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>126189623</v>
       </c>
       <c r="B19" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>126189622</v>
       </c>
       <c r="B20" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>126189624</v>
       </c>
       <c r="B21" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>126189627</v>
       </c>
       <c r="B22" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>126189591</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>126189625</v>
       </c>
       <c r="B24" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3186,42 +3186,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126189664</v>
+        <v>126189620</v>
       </c>
       <c r="B25" t="n">
-        <v>80075</v>
+        <v>98341</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583097</v>
+        <v>583033</v>
       </c>
       <c r="R25" t="n">
-        <v>6968518</v>
+        <v>6968690</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3275,12 +3275,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt på sälg</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3307,42 +3302,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126189620</v>
+        <v>126189664</v>
       </c>
       <c r="B26" t="n">
-        <v>98339</v>
+        <v>80076</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3351,10 +3346,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583033</v>
+        <v>583097</v>
       </c>
       <c r="R26" t="n">
-        <v>6968690</v>
+        <v>6968518</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3386,7 +3381,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3396,7 +3391,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt på sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3426,7 +3426,7 @@
         <v>126189661</v>
       </c>
       <c r="B27" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>126189621</v>
       </c>
       <c r="B28" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>126189628</v>
       </c>
       <c r="B29" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -2004,7 +2004,7 @@
         <v>126189733</v>
       </c>
       <c r="B15" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>126189626</v>
       </c>
       <c r="B16" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>126189623</v>
       </c>
       <c r="B19" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>126189622</v>
       </c>
       <c r="B20" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>126189624</v>
       </c>
       <c r="B21" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>126189627</v>
       </c>
       <c r="B22" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>126189625</v>
       </c>
       <c r="B24" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3186,42 +3186,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126189620</v>
+        <v>126189664</v>
       </c>
       <c r="B25" t="n">
-        <v>98341</v>
+        <v>80076</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583033</v>
+        <v>583097</v>
       </c>
       <c r="R25" t="n">
-        <v>6968690</v>
+        <v>6968518</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3275,7 +3275,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt på sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3302,42 +3307,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126189664</v>
+        <v>126189620</v>
       </c>
       <c r="B26" t="n">
-        <v>80076</v>
+        <v>98343</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3346,10 +3351,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583097</v>
+        <v>583033</v>
       </c>
       <c r="R26" t="n">
-        <v>6968518</v>
+        <v>6968690</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3381,7 +3386,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3391,12 +3396,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt på sälg</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3547,7 +3547,7 @@
         <v>126189621</v>
       </c>
       <c r="B28" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>126189628</v>
       </c>
       <c r="B29" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -2004,7 +2004,7 @@
         <v>126189733</v>
       </c>
       <c r="B15" t="n">
-        <v>91236</v>
+        <v>91238</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>126189626</v>
       </c>
       <c r="B16" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>126189623</v>
       </c>
       <c r="B19" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>126189622</v>
       </c>
       <c r="B20" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>126189624</v>
       </c>
       <c r="B21" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>126189627</v>
       </c>
       <c r="B22" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>126189625</v>
       </c>
       <c r="B24" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>126189620</v>
       </c>
       <c r="B26" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>126189621</v>
       </c>
       <c r="B28" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>126189628</v>
       </c>
       <c r="B29" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -2004,7 +2004,7 @@
         <v>126189733</v>
       </c>
       <c r="B15" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>126189626</v>
       </c>
       <c r="B16" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>126189663</v>
       </c>
       <c r="B17" t="n">
-        <v>80111</v>
+        <v>80115</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>126189590</v>
       </c>
       <c r="B18" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>126189623</v>
       </c>
       <c r="B19" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>126189622</v>
       </c>
       <c r="B20" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>126189624</v>
       </c>
       <c r="B21" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>126189627</v>
       </c>
       <c r="B22" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>126189591</v>
       </c>
       <c r="B23" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>126189625</v>
       </c>
       <c r="B24" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>126189664</v>
       </c>
       <c r="B25" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>126189620</v>
       </c>
       <c r="B26" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>126189661</v>
       </c>
       <c r="B27" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>126189621</v>
       </c>
       <c r="B28" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>126189628</v>
       </c>
       <c r="B29" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -2120,7 +2120,7 @@
         <v>126189626</v>
       </c>
       <c r="B16" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>126189623</v>
       </c>
       <c r="B19" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>126189622</v>
       </c>
       <c r="B20" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>126189624</v>
       </c>
       <c r="B21" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>126189627</v>
       </c>
       <c r="B22" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>126189625</v>
       </c>
       <c r="B24" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>126189620</v>
       </c>
       <c r="B26" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>126189621</v>
       </c>
       <c r="B28" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>126189628</v>
       </c>
       <c r="B29" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -3186,42 +3186,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126189664</v>
+        <v>126189620</v>
       </c>
       <c r="B25" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583097</v>
+        <v>583033</v>
       </c>
       <c r="R25" t="n">
-        <v>6968518</v>
+        <v>6968690</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3275,12 +3275,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt på sälg</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3307,42 +3302,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126189620</v>
+        <v>126189664</v>
       </c>
       <c r="B26" t="n">
-        <v>98352</v>
+        <v>80080</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3351,10 +3346,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583033</v>
+        <v>583097</v>
       </c>
       <c r="R26" t="n">
-        <v>6968690</v>
+        <v>6968518</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3386,7 +3381,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3396,7 +3391,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt på sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -2004,7 +2004,7 @@
         <v>126189733</v>
       </c>
       <c r="B15" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>126189626</v>
       </c>
       <c r="B16" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>126189663</v>
       </c>
       <c r="B17" t="n">
-        <v>80115</v>
+        <v>80118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>126189590</v>
       </c>
       <c r="B18" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>126189623</v>
       </c>
       <c r="B19" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>126189622</v>
       </c>
       <c r="B20" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>126189624</v>
       </c>
       <c r="B21" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>126189627</v>
       </c>
       <c r="B22" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2947,7 +2947,7 @@
         <v>126189591</v>
       </c>
       <c r="B23" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>126189625</v>
       </c>
       <c r="B24" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3186,42 +3186,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126189620</v>
+        <v>126189664</v>
       </c>
       <c r="B25" t="n">
-        <v>98352</v>
+        <v>80083</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583033</v>
+        <v>583097</v>
       </c>
       <c r="R25" t="n">
-        <v>6968690</v>
+        <v>6968518</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3275,7 +3275,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt på sälg</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3302,42 +3307,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126189664</v>
+        <v>126189620</v>
       </c>
       <c r="B26" t="n">
-        <v>80080</v>
+        <v>98361</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3346,10 +3351,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583097</v>
+        <v>583033</v>
       </c>
       <c r="R26" t="n">
-        <v>6968518</v>
+        <v>6968690</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3381,7 +3386,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3391,12 +3396,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt på sälg</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3426,7 +3426,7 @@
         <v>126189661</v>
       </c>
       <c r="B27" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
         <v>126189621</v>
       </c>
       <c r="B28" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>126189628</v>
       </c>
       <c r="B29" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -3186,42 +3186,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126189664</v>
+        <v>126189620</v>
       </c>
       <c r="B25" t="n">
-        <v>80083</v>
+        <v>98361</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3230,10 +3230,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583097</v>
+        <v>583033</v>
       </c>
       <c r="R25" t="n">
-        <v>6968518</v>
+        <v>6968690</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3275,12 +3275,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt på sälg</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3307,42 +3302,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126189620</v>
+        <v>126189664</v>
       </c>
       <c r="B26" t="n">
-        <v>98361</v>
+        <v>80083</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3351,10 +3346,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583033</v>
+        <v>583097</v>
       </c>
       <c r="R26" t="n">
-        <v>6968690</v>
+        <v>6968518</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3386,7 +3381,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3396,7 +3391,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Rikligt på sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4702,6 +4702,247 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>133527175</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Storfloåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>583062</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6968780</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>06:38</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>06:38</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Fyndet gjordes under inventering inom Svenska Kraftnäts projekt Inlandspaketet.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>133527173</v>
+      </c>
+      <c r="B40" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Storfloåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>583082</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6968831</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>06:35</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>06:35</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Fyndet gjordes under inventering inom Svenska Kraftnäts projekt Inlandspaketet.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -3781,45 +3781,55 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133153671</v>
+        <v>133153966</v>
       </c>
       <c r="B30" t="n">
-        <v>79333</v>
+        <v>58502</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>102990</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583090</v>
+        <v>583051</v>
       </c>
       <c r="R30" t="n">
-        <v>6968898</v>
+        <v>6968649</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3846,12 +3856,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3878,55 +3888,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133153966</v>
+        <v>133153671</v>
       </c>
       <c r="B31" t="n">
-        <v>58502</v>
+        <v>79333</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102990</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583051</v>
+        <v>583090</v>
       </c>
       <c r="R31" t="n">
-        <v>6968649</v>
+        <v>6968898</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3953,12 +3953,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -3781,55 +3781,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133153966</v>
+        <v>133153671</v>
       </c>
       <c r="B30" t="n">
-        <v>58502</v>
+        <v>79333</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102990</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583051</v>
+        <v>583090</v>
       </c>
       <c r="R30" t="n">
-        <v>6968649</v>
+        <v>6968898</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3856,12 +3846,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3888,45 +3878,55 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133153671</v>
+        <v>133153966</v>
       </c>
       <c r="B31" t="n">
-        <v>79333</v>
+        <v>58502</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>102990</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583090</v>
+        <v>583051</v>
       </c>
       <c r="R31" t="n">
-        <v>6968898</v>
+        <v>6968649</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3953,12 +3953,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -3784,7 +3784,7 @@
         <v>133153671</v>
       </c>
       <c r="B30" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>133153528</v>
       </c>
       <c r="B32" t="n">
-        <v>91918</v>
+        <v>91920</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>133153674</v>
       </c>
       <c r="B35" t="n">
-        <v>83181</v>
+        <v>83182</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>133153670</v>
       </c>
       <c r="B37" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>133527175</v>
       </c>
       <c r="B39" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>133527173</v>
       </c>
       <c r="B40" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -3988,7 +3988,7 @@
         <v>133153528</v>
       </c>
       <c r="B32" t="n">
-        <v>91920</v>
+        <v>91928</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>133153674</v>
       </c>
       <c r="B35" t="n">
-        <v>83182</v>
+        <v>83183</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>133527175</v>
       </c>
       <c r="B39" t="n">
-        <v>99132</v>
+        <v>99140</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -3781,45 +3781,55 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133153671</v>
+        <v>133153966</v>
       </c>
       <c r="B30" t="n">
-        <v>79334</v>
+        <v>58509</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>102990</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583090</v>
+        <v>583051</v>
       </c>
       <c r="R30" t="n">
-        <v>6968898</v>
+        <v>6968649</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3846,12 +3856,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3878,55 +3888,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133153966</v>
+        <v>133153671</v>
       </c>
       <c r="B31" t="n">
-        <v>58502</v>
+        <v>79348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102990</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583051</v>
+        <v>583090</v>
       </c>
       <c r="R31" t="n">
-        <v>6968649</v>
+        <v>6968898</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3953,12 +3953,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3988,7 +3988,7 @@
         <v>133153528</v>
       </c>
       <c r="B32" t="n">
-        <v>91928</v>
+        <v>91947</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>133154053</v>
       </c>
       <c r="B33" t="n">
-        <v>58641</v>
+        <v>58648</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>133153967</v>
       </c>
       <c r="B34" t="n">
-        <v>58502</v>
+        <v>58509</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>133153674</v>
       </c>
       <c r="B35" t="n">
-        <v>83183</v>
+        <v>83197</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>133153761</v>
       </c>
       <c r="B36" t="n">
-        <v>58393</v>
+        <v>58400</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>133153670</v>
       </c>
       <c r="B37" t="n">
-        <v>79334</v>
+        <v>79348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>133153757</v>
       </c>
       <c r="B38" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>133527175</v>
       </c>
       <c r="B39" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>133527173</v>
       </c>
       <c r="B40" t="n">
-        <v>80439</v>
+        <v>80453</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -4707,7 +4707,7 @@
         <v>133527175</v>
       </c>
       <c r="B39" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>133527173</v>
       </c>
       <c r="B40" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -4707,7 +4707,7 @@
         <v>133527175</v>
       </c>
       <c r="B39" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         <v>133527173</v>
       </c>
       <c r="B40" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112538743</v>
+        <v>112538744</v>
       </c>
       <c r="B2" t="n">
-        <v>90101</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112538746</v>
+        <v>126189733</v>
       </c>
       <c r="B3" t="n">
-        <v>77746</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +783,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Källmyrberget, Mpd</t>
+          <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583063</v>
+        <v>583010</v>
       </c>
       <c r="R3" t="n">
-        <v>6968612</v>
+        <v>6968843</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +846,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,62 +876,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112538736</v>
+        <v>133153528</v>
       </c>
       <c r="B4" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Källmyrberget, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583060</v>
+        <v>583143</v>
       </c>
       <c r="R4" t="n">
-        <v>6968784</v>
+        <v>6968584</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,49 +973,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112538737</v>
+        <v>112538743</v>
       </c>
       <c r="B5" t="n">
-        <v>78836</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583094</v>
+        <v>583123</v>
       </c>
       <c r="R5" t="n">
-        <v>6968738</v>
+        <v>6968652</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1082,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112538744</v>
+        <v>133153674</v>
       </c>
       <c r="B6" t="n">
-        <v>89942</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83222</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1099,34 +1093,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Källmyrberget, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583123</v>
+        <v>583088</v>
       </c>
       <c r="R6" t="n">
-        <v>6968652</v>
+        <v>6968845</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,12 +1147,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,49 +1167,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112538745</v>
+        <v>112538735</v>
       </c>
       <c r="B7" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1214,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583139</v>
+        <v>583026</v>
       </c>
       <c r="R7" t="n">
-        <v>6968648</v>
+        <v>6968783</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,37 +1276,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112538742</v>
+        <v>112538746</v>
       </c>
       <c r="B8" t="n">
-        <v>57490</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583054</v>
+        <v>583063</v>
       </c>
       <c r="R8" t="n">
-        <v>6968671</v>
+        <v>6968612</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,15 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112538741</v>
+        <v>133153670</v>
       </c>
       <c r="B9" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,34 +1384,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Källmyrberget, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583053</v>
+        <v>583088</v>
       </c>
       <c r="R9" t="n">
-        <v>6968671</v>
+        <v>6968845</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,12 +1438,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,62 +1458,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112538735</v>
+        <v>133153671</v>
       </c>
       <c r="B10" t="n">
-        <v>89625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källmyrberget, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583026</v>
+        <v>583090</v>
       </c>
       <c r="R10" t="n">
-        <v>6968783</v>
+        <v>6968898</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,12 +1535,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1581,12 +1555,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1596,12 +1570,7 @@
         <v>112538747</v>
       </c>
       <c r="B11" t="n">
-        <v>78809</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1695,53 +1664,57 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112538738</v>
+        <v>126189661</v>
       </c>
       <c r="B12" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Källmyrberget, Mpd</t>
+          <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583026</v>
+        <v>583067</v>
       </c>
       <c r="R12" t="n">
-        <v>6968679</v>
+        <v>6968526</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1765,12 +1738,27 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 10x10 cm bål på björk</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1785,65 +1773,69 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>112538740</v>
+        <v>126189664</v>
       </c>
       <c r="B13" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Källmyrberget, Mpd</t>
+          <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583041</v>
+        <v>583097</v>
       </c>
       <c r="R13" t="n">
-        <v>6968672</v>
+        <v>6968518</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1867,12 +1859,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt på sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1887,62 +1894,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112538734</v>
+        <v>133527173</v>
       </c>
       <c r="B14" t="n">
-        <v>96886</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Källmyrberget, Mpd</t>
+          <t>Storfloåsen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583096</v>
+        <v>583082</v>
       </c>
       <c r="R14" t="n">
-        <v>6968834</v>
+        <v>6968831</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,12 +1971,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>06:35</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-10-03</t>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>06:35</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Fyndet gjordes under inventering inom Svenska Kraftnäts projekt Inlandspaketet.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1989,69 +2006,64 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Elijah Ourth</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Elijah Ourth</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126189733</v>
+        <v>112538737</v>
       </c>
       <c r="B15" t="n">
-        <v>91245</v>
+        <v>80461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sundsvall Västanå, Mpd</t>
+          <t>Källmyrberget, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583010</v>
+        <v>583094</v>
       </c>
       <c r="R15" t="n">
-        <v>6968843</v>
+        <v>6968738</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2075,22 +2087,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:29</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:29</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2105,54 +2107,54 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126189626</v>
+        <v>126189663</v>
       </c>
       <c r="B16" t="n">
-        <v>98361</v>
+        <v>80467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>cm²</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2161,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583055</v>
+        <v>583097</v>
       </c>
       <c r="R16" t="n">
-        <v>6968770</v>
+        <v>6968518</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2196,7 +2198,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2206,7 +2208,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ca 3x5cm bål</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2233,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126189663</v>
+        <v>133153757</v>
       </c>
       <c r="B17" t="n">
-        <v>80118</v>
+        <v>57972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2244,46 +2251,47 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>cm²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sundsvall Västanå, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583097</v>
+        <v>582984</v>
       </c>
       <c r="R17" t="n">
-        <v>6968518</v>
+        <v>6968885</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2307,27 +2315,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>14:04</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ca 3x5cm bål</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2342,22 +2335,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126189590</v>
+        <v>112538742</v>
       </c>
       <c r="B18" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2382,34 +2375,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sundsvall Västanå, Mpd</t>
+          <t>Källmyrberget, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583048</v>
+        <v>583054</v>
       </c>
       <c r="R18" t="n">
-        <v>6968633</v>
+        <v>6968671</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2433,27 +2412,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:22</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2468,54 +2432,59 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126189623</v>
+        <v>126189590</v>
       </c>
       <c r="B19" t="n">
-        <v>98361</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2524,10 +2493,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583115</v>
+        <v>583048</v>
       </c>
       <c r="R19" t="n">
-        <v>6968621</v>
+        <v>6968633</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2559,7 +2528,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2569,7 +2538,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2596,42 +2570,47 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126189622</v>
+        <v>126189591</v>
       </c>
       <c r="B20" t="n">
-        <v>98361</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2640,10 +2619,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583019</v>
+        <v>583075</v>
       </c>
       <c r="R20" t="n">
-        <v>6968674</v>
+        <v>6968803</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2675,7 +2654,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2685,7 +2664,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2712,57 +2696,58 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126189624</v>
+        <v>133153966</v>
       </c>
       <c r="B21" t="n">
-        <v>98361</v>
+        <v>58519</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>102990</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sundsvall Västanå, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583110</v>
+        <v>583051</v>
       </c>
       <c r="R21" t="n">
-        <v>6968680</v>
+        <v>6968649</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2786,22 +2771,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>13:49</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2816,69 +2791,70 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126189627</v>
+        <v>133153967</v>
       </c>
       <c r="B22" t="n">
-        <v>98361</v>
+        <v>58519</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>102990</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sundsvall Västanå, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583059</v>
+        <v>583047</v>
       </c>
       <c r="R22" t="n">
-        <v>6968767</v>
+        <v>6968865</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2902,22 +2878,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>13:38</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2932,22 +2898,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126189591</v>
+        <v>133153761</v>
       </c>
       <c r="B23" t="n">
-        <v>57657</v>
+        <v>58410</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2955,31 +2921,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2989,17 +2951,17 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sundsvall Västanå, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583075</v>
+        <v>583033</v>
       </c>
       <c r="R23" t="n">
-        <v>6968803</v>
+        <v>6968692</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3023,27 +2985,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:35</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3058,69 +3005,70 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126189625</v>
+        <v>133153926</v>
       </c>
       <c r="B24" t="n">
-        <v>98361</v>
+        <v>58349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sundsvall Västanå, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583049</v>
+        <v>583026</v>
       </c>
       <c r="R24" t="n">
-        <v>6968768</v>
+        <v>6968543</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3144,22 +3092,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>13:42</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3174,69 +3112,70 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126189620</v>
+        <v>133153696</v>
       </c>
       <c r="B25" t="n">
-        <v>98361</v>
+        <v>58131</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103023</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sundsvall Västanå, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583033</v>
+        <v>583051</v>
       </c>
       <c r="R25" t="n">
-        <v>6968690</v>
+        <v>6968543</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3260,22 +3199,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:33</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:33</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3290,69 +3219,70 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126189664</v>
+        <v>133154053</v>
       </c>
       <c r="B26" t="n">
-        <v>80083</v>
+        <v>58658</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>103044</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sundsvall Västanå, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583097</v>
+        <v>583046</v>
       </c>
       <c r="R26" t="n">
-        <v>6968518</v>
+        <v>6968828</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3376,27 +3306,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:03</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt på sälg</t>
+          <t>2024-07-06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3411,69 +3326,60 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126189661</v>
+        <v>133153640</v>
       </c>
       <c r="B27" t="n">
-        <v>80083</v>
+        <v>108274</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>220102</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sundsvall Västanå, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583067</v>
+        <v>583139</v>
       </c>
       <c r="R27" t="n">
-        <v>6968526</v>
+        <v>6968491</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3497,27 +3403,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:14</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:14</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ca 10x10 cm bål på björk</t>
+          <t>2024-06-12</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3532,22 +3423,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126189621</v>
+        <v>112538734</v>
       </c>
       <c r="B28" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3572,29 +3463,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sundsvall Västanå, Mpd</t>
+          <t>Källmyrberget, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583027</v>
+        <v>583097</v>
       </c>
       <c r="R28" t="n">
-        <v>6968681</v>
+        <v>6968834</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3618,22 +3500,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3648,22 +3520,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126189628</v>
+        <v>112538736</v>
       </c>
       <c r="B29" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3688,29 +3560,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sundsvall Västanå, Mpd</t>
+          <t>Källmyrberget, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583041</v>
+        <v>583060</v>
       </c>
       <c r="R29" t="n">
-        <v>6968875</v>
+        <v>6968784</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3734,27 +3597,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-11</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:24</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ca 1x1m smockfullt</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3769,67 +3617,57 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Joseph Anderson</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133153966</v>
+        <v>112538738</v>
       </c>
       <c r="B30" t="n">
-        <v>58509</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102990</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Källmyrberget, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>583051</v>
+        <v>583026</v>
       </c>
       <c r="R30" t="n">
-        <v>6968649</v>
+        <v>6968679</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3856,12 +3694,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3876,57 +3714,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133153671</v>
+        <v>112538740</v>
       </c>
       <c r="B31" t="n">
-        <v>79348</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Källmyrberget, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583090</v>
+        <v>583041</v>
       </c>
       <c r="R31" t="n">
-        <v>6968898</v>
+        <v>6968672</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3953,12 +3791,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3973,57 +3811,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133153528</v>
+        <v>112538741</v>
       </c>
       <c r="B32" t="n">
-        <v>91947</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Källmyrberget, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583143</v>
+        <v>583054</v>
       </c>
       <c r="R32" t="n">
-        <v>6968584</v>
+        <v>6968671</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4050,12 +3888,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4070,67 +3908,57 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133154053</v>
+        <v>112538745</v>
       </c>
       <c r="B33" t="n">
-        <v>58648</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103044</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Källmyrberget, Mpd</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583046</v>
+        <v>583139</v>
       </c>
       <c r="R33" t="n">
-        <v>6968828</v>
+        <v>6968648</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4157,12 +3985,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2023-10-03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4177,70 +4005,69 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133153967</v>
+        <v>126189620</v>
       </c>
       <c r="B34" t="n">
-        <v>58509</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102990</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583047</v>
+        <v>583033</v>
       </c>
       <c r="R34" t="n">
-        <v>6968865</v>
+        <v>6968690</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4264,12 +4091,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4284,60 +4121,69 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133153674</v>
+        <v>126189621</v>
       </c>
       <c r="B35" t="n">
-        <v>83197</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583088</v>
+        <v>583027</v>
       </c>
       <c r="R35" t="n">
-        <v>6968845</v>
+        <v>6968681</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4361,12 +4207,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4381,70 +4237,69 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133153761</v>
+        <v>126189622</v>
       </c>
       <c r="B36" t="n">
-        <v>58400</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103001</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583033</v>
+        <v>583019</v>
       </c>
       <c r="R36" t="n">
-        <v>6968692</v>
+        <v>6968674</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4468,12 +4323,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4488,60 +4353,69 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133153670</v>
+        <v>126189623</v>
       </c>
       <c r="B37" t="n">
-        <v>79348</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>583088</v>
+        <v>583115</v>
       </c>
       <c r="R37" t="n">
-        <v>6968845</v>
+        <v>6968621</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4565,12 +4439,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-06-12</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4585,70 +4469,69 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133153757</v>
+        <v>126189624</v>
       </c>
       <c r="B38" t="n">
-        <v>57962</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>582984</v>
+        <v>583110</v>
       </c>
       <c r="R38" t="n">
-        <v>6968885</v>
+        <v>6968680</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4672,12 +4555,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4692,22 +4585,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133527175</v>
+        <v>126189625</v>
       </c>
       <c r="B39" t="n">
-        <v>99181</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4734,27 +4627,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storfloåsen, Mpd</t>
+          <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583062</v>
+        <v>583049</v>
       </c>
       <c r="R39" t="n">
-        <v>6968780</v>
+        <v>6968768</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4778,27 +4671,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>06:38</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>06:38</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Fyndet gjordes under inventering inom Svenska Kraftnäts projekt Inlandspaketet.</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4813,64 +4701,69 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
+          <t>Joseph Anderson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Elijah Ourth</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133527173</v>
+        <v>126189626</v>
       </c>
       <c r="B40" t="n">
-        <v>80474</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storfloåsen, Mpd</t>
+          <t>Sundsvall Västanå, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583082</v>
+        <v>583055</v>
       </c>
       <c r="R40" t="n">
-        <v>6968831</v>
+        <v>6968770</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4894,27 +4787,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>06:35</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>06:35</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Fyndet gjordes under inventering inom Svenska Kraftnäts projekt Inlandspaketet.</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4929,19 +4817,571 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126189627</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>583059</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6968767</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126189628</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Sundsvall Västanå, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>583041</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6968875</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-11</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ca 1x1m smockfullt</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joseph Anderson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>133527175</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Storfloåsen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>583062</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6968780</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>06:38</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>06:38</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Fyndet gjordes under inventering inom Svenska Kraftnäts projekt Inlandspaketet.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
           <t>Elijah Ourth</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
+      <c r="AX43" t="inlineStr">
         <is>
           <t>Elijah Ourth</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr">
+      <c r="AY43" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>
       </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>133153605</v>
+      </c>
+      <c r="B44" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Järkvissle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>583183</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6968506</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>133153616</v>
+      </c>
+      <c r="B45" t="n">
+        <v>101293</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Järkvissle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>583122</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6968961</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49327-2023 artfynd.xlsx
+++ b/artfynd/A 49327-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538744</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189733</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153528</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1079,6 +1099,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538743</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1176,6 +1201,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153674</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1273,6 +1303,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538735</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1370,6 +1405,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538746</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1467,6 +1507,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153670</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1564,6 +1609,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153671</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1661,6 +1711,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538747</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1782,6 +1837,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189661</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1903,6 +1963,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189664</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2019,6 +2084,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133527173</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2116,6 +2186,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538737</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2237,6 +2312,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189663</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2344,6 +2424,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153757</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2441,6 +2526,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538742</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2567,6 +2657,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189590</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2693,6 +2788,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189591</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2800,6 +2900,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153966</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2907,6 +3012,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153967</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3014,6 +3124,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153761</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3121,6 +3236,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153926</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3228,6 +3348,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153696</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3335,6 +3460,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133154053</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3432,6 +3562,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153640</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3529,6 +3664,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538734</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3626,6 +3766,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538736</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3723,6 +3868,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538738</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3820,6 +3970,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538740</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3917,6 +4072,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538741</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4014,6 +4174,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112538745</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4130,6 +4295,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189620</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4246,6 +4416,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189621</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4362,6 +4537,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189622</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4478,6 +4658,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189623</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4594,6 +4779,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189624</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4710,6 +4900,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189625</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4826,6 +5021,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189626</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4942,6 +5142,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189627</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5063,6 +5268,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126189628</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5188,6 +5398,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133527175</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5285,6 +5500,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153605</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5382,8 +5602,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133153616</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>